--- a/databases/teste_stuart_maxwell.xlsx
+++ b/databases/teste_stuart_maxwell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\OneDrive - Universidade Federal do Espírito Santo\Documentos\Artigo_aborto\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_2E63FDCE8F79A8D366075C52F3EE3231BFF6CEF2" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{57E04267-67AD-4B50-BC3B-79FE1CF8DEE6}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_4D62FDCE8F79A8D366075C52F31F9A71FA02E6D4" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{EB67E5B3-9608-4F02-9430-9E82A9B072A3}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
   <si>
     <t>P-value</t>
   </si>
@@ -31,10 +31,13 @@
     <t>Private healthcare and insurance, years 2017 to 2019 vs. years 2022 to 2024</t>
   </si>
   <si>
+    <t>0.6717</t>
+  </si>
+  <si>
+    <t>Brazilian Unified Health System (SUS), years 2017 to 2019 vs. years 2022 to 2024</t>
+  </si>
+  <si>
     <t>&lt; 0.0001</t>
-  </si>
-  <si>
-    <t>Brazilian Unified Health System (SUS), years 2017 to 2019 vs. years 2022 to 2024</t>
   </si>
   <si>
     <t>Years 2017 to 2019, private healthcare and insurance vs. Brazilian Unified Health System (SUS)</t>
@@ -50,7 +53,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -60,6 +63,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -87,11 +98,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,16 +442,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="82.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="82.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -456,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>3212.0803000000001</v>
+        <v>0.79590000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -464,33 +477,36 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>1354.6353999999999</v>
+        <v>63.869199999999999</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
       <c r="C4">
-        <v>920.80039999999997</v>
+        <v>670.0258</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>3251.2215000000001</v>
-      </c>
+        <v>542.16600000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
